--- a/scripts/ground-truth/judah-2026-05-16-oufc.xlsx
+++ b/scripts/ground-truth/judah-2026-05-16-oufc.xlsx
@@ -1320,7 +1320,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>70</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>74</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>89</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>96</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>99</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>103</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>103</v>
       </c>
@@ -2937,7 +2937,6 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>110</v>
@@ -3018,8 +3017,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>60</v>
@@ -3055,7 +3052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>128</v>
       </c>
@@ -3081,7 +3078,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>133</v>
       </c>
@@ -3107,7 +3104,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>139</v>
       </c>
@@ -3130,7 +3127,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>141</v>
       </c>
@@ -3153,7 +3150,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>142</v>
       </c>
@@ -3176,7 +3173,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>143</v>
       </c>
@@ -3202,7 +3199,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>146</v>
       </c>
@@ -3225,7 +3222,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>147</v>
       </c>
@@ -3248,7 +3245,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>150</v>
       </c>
@@ -3271,7 +3268,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>99</v>
       </c>
@@ -3294,7 +3291,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>151</v>
       </c>
